--- a/feedback_surveys/020_resolution_time_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/020_resolution_time_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>support_team_lead</t>
+          <t>support_team_lead_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Support Team Lead</t>
+          <t>Support Team Lead 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>support_team_lead_email</t>
+          <t>support_team_lead_email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Support Team Lead Email</t>
+          <t>Support Team Lead Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>support_team_lead_phone</t>
+          <t>support_team_lead_phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support Team Lead Phone</t>
+          <t>Support Team Lead Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on_time',_'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On Time', 'value': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late',_'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late', 'value': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_response',_'value':_'no_response'}</t>
+          <t>no_response</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No Response', 'value': 'No Response'}</t>
+          <t>No Response</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on_hold',_'value':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On Hold', 'value': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'done',_'value':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Done', 'value': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'unknown',_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Unknown', 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
